--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$185</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7240" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6941" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1799,59 +1799,7 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].code</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -2012,28 +1960,56 @@
     <t>Observation.component:predicted.value[x]</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity</t>
   </si>
   <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
   </si>
   <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
   </si>
   <si>
+    <t>Observation.component.value[x].value</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
+    <t>Observation.component.value[x].comparator</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
+    <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
   </si>
   <si>
+    <t>Observation.component.value[x].system</t>
+  </si>
+  <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].code</t>
   </si>
   <si>
     <t>Observation.component:predicted.dataAbsentReason</t>
@@ -2562,7 +2538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO193"/>
+  <dimension ref="A1:AO185"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.09765625" customWidth="true" bestFit="true"/>
@@ -12786,14 +12762,16 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC87" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>564</v>
@@ -12814,7 +12792,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>391</v>
@@ -12828,14 +12806,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12853,22 +12829,22 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12893,13 +12869,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12917,7 +12893,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12926,7 +12902,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -12935,35 +12911,35 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>81</v>
@@ -12975,16 +12951,20 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -13008,13 +12988,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -13032,46 +13012,46 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13090,18 +13070,20 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13137,19 +13119,19 @@
         <v>81</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13161,7 +13143,7 @@
         <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>81</v>
@@ -13170,7 +13152,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13181,12 +13163,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13207,19 +13191,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>397</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>398</v>
+        <v>583</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13268,13 +13252,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -13289,7 +13273,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13300,10 +13284,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13320,30 +13304,26 @@
         <v>81</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q92" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
         <v>81</v>
       </c>
@@ -13363,13 +13343,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -13387,7 +13367,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13399,7 +13379,7 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -13408,7 +13388,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13417,46 +13397,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -13504,19 +13484,19 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
@@ -13525,7 +13505,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -13534,45 +13514,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O94" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13621,19 +13603,19 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -13642,7 +13624,7 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
@@ -13651,12 +13633,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13664,13 +13646,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>81</v>
@@ -13679,19 +13661,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13716,13 +13698,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13740,10 +13722,10 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
@@ -13758,13 +13740,13 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13772,10 +13754,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13798,20 +13780,16 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13835,13 +13813,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13859,7 +13837,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13868,10 +13846,10 @@
         <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
@@ -13880,7 +13858,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -13891,14 +13869,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13917,20 +13895,18 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13954,31 +13930,31 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13990,30 +13966,30 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14033,22 +14009,22 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -14085,19 +14061,17 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14118,7 +14092,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -14129,13 +14103,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>598</v>
+        <v>274</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>81</v>
@@ -14157,19 +14131,19 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>275</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>276</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14179,7 +14153,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14218,7 +14192,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14239,7 +14213,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -14250,10 +14224,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14365,10 +14339,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14438,16 +14412,16 @@
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>118</v>
@@ -14482,45 +14456,45 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>503</v>
+        <v>284</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14569,19 +14543,19 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>505</v>
+        <v>288</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>81</v>
@@ -14590,7 +14564,7 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
@@ -14601,10 +14575,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14612,7 +14586,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>91</v>
@@ -14627,20 +14601,18 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>560</v>
+        <v>292</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>561</v>
+        <v>293</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14664,13 +14636,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14688,10 +14660,10 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>295</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>91</v>
@@ -14706,13 +14678,13 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14720,10 +14692,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14743,19 +14715,21 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14779,13 +14753,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14803,7 +14775,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14815,7 +14787,7 @@
         <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>81</v>
@@ -14824,7 +14796,7 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
@@ -14835,21 +14807,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14858,21 +14830,21 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14908,31 +14880,31 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>81</v>
@@ -14941,7 +14913,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -14952,10 +14924,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14966,7 +14938,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14978,19 +14950,19 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -15027,23 +14999,25 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC106" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>81</v>
@@ -15058,7 +15032,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -15069,13 +15043,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
@@ -15100,10 +15074,10 @@
         <v>144</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>245</v>
@@ -15119,7 +15093,7 @@
         <v>81</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>81</v>
@@ -15134,13 +15108,11 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -15190,10 +15162,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15305,10 +15277,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15422,10 +15394,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15541,10 +15513,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15658,10 +15630,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15723,7 +15695,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15773,10 +15745,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15890,10 +15862,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16007,16 +15979,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16028,7 +15998,7 @@
         <v>91</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>81</v>
@@ -16037,19 +16007,19 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -16074,11 +16044,13 @@
         <v>81</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>81</v>
@@ -16096,13 +16068,13 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>81</v>
@@ -16117,7 +16089,7 @@
         <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16128,10 +16100,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16151,19 +16123,23 @@
         <v>81</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16199,19 +16175,17 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16223,41 +16197,43 @@
         <v>81</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="D117" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
@@ -16266,21 +16242,23 @@
         <v>81</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16316,54 +16294,54 @@
         <v>81</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16383,23 +16361,19 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16447,7 +16421,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16459,7 +16433,7 @@
         <v>81</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>81</v>
@@ -16468,7 +16442,7 @@
         <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>81</v>
@@ -16479,21 +16453,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16502,19 +16476,19 @@
         <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>294</v>
+        <v>114</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16552,31 +16526,31 @@
         <v>81</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>295</v>
+        <v>118</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>81</v>
@@ -16585,7 +16559,7 @@
         <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>81</v>
@@ -16594,12 +16568,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16613,7 +16587,7 @@
         <v>91</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>81</v>
@@ -16622,17 +16596,19 @@
         <v>92</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>299</v>
+        <v>397</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16657,11 +16633,13 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
@@ -16679,7 +16657,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16700,7 +16678,7 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
@@ -16711,10 +16689,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16731,28 +16709,30 @@
         <v>81</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J121" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16772,13 +16752,13 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16796,7 +16776,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16817,7 +16797,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16826,12 +16806,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16845,7 +16825,7 @@
         <v>91</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>81</v>
@@ -16854,19 +16834,17 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16876,7 +16854,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16915,7 +16893,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16936,7 +16914,7 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
@@ -16945,12 +16923,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16964,7 +16942,7 @@
         <v>91</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>81</v>
@@ -16973,19 +16951,17 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16995,7 +16971,7 @@
         <v>81</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>81</v>
@@ -17034,7 +17010,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17043,7 +17019,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>103</v>
@@ -17055,7 +17031,7 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
@@ -17064,12 +17040,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17083,7 +17059,7 @@
         <v>91</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>81</v>
@@ -17092,19 +17068,19 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>565</v>
+        <v>166</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>566</v>
+        <v>427</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>567</v>
+        <v>428</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>568</v>
+        <v>429</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17114,7 +17090,7 @@
         <v>81</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>81</v>
@@ -17141,17 +17117,19 @@
         <v>81</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC124" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17169,16 +17147,16 @@
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" hidden="true">
@@ -17186,11 +17164,9 @@
         <v>638</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17208,22 +17184,22 @@
         <v>81</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17248,13 +17224,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -17272,7 +17248,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17281,7 +17257,7 @@
         <v>91</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>103</v>
@@ -17290,16 +17266,16 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -17311,14 +17287,14 @@
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17330,16 +17306,20 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17363,13 +17343,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17387,34 +17367,34 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -17422,11 +17402,11 @@
         <v>640</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -17445,18 +17425,20 @@
         <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
       </c>
@@ -17492,19 +17474,19 @@
         <v>81</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17516,7 +17498,7 @@
         <v>81</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>81</v>
@@ -17525,7 +17507,7 @@
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>81</v>
@@ -17534,14 +17516,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>641</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>642</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17553,7 +17537,7 @@
         <v>91</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>81</v>
@@ -17562,19 +17546,19 @@
         <v>92</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>397</v>
+        <v>643</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>398</v>
+        <v>644</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17623,13 +17607,13 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>81</v>
@@ -17644,7 +17628,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -17655,10 +17639,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17675,30 +17659,26 @@
         <v>81</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q129" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17718,13 +17698,13 @@
         <v>81</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>81</v>
@@ -17742,7 +17722,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17754,7 +17734,7 @@
         <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>81</v>
@@ -17763,7 +17743,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -17774,21 +17754,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -17797,21 +17777,21 @@
         <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17820,7 +17800,7 @@
         <v>81</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>81</v>
@@ -17859,19 +17839,19 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>81</v>
@@ -17880,7 +17860,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -17891,43 +17871,45 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O131" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -17937,7 +17919,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17976,19 +17958,19 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>81</v>
@@ -17997,7 +17979,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18008,10 +17990,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18019,7 +18001,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>91</v>
@@ -18034,19 +18016,19 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
@@ -18056,7 +18038,7 @@
         <v>81</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>81</v>
@@ -18071,13 +18053,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -18095,10 +18077,10 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>91</v>
@@ -18113,13 +18095,13 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18127,10 +18109,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18153,20 +18135,16 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18190,13 +18168,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18214,7 +18192,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18223,10 +18201,10 @@
         <v>91</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>81</v>
@@ -18235,7 +18213,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18246,14 +18224,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18272,20 +18250,18 @@
         <v>81</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18309,31 +18285,31 @@
         <v>81</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18345,30 +18321,30 @@
         <v>81</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18388,22 +18364,22 @@
         <v>81</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18440,19 +18416,17 @@
         <v>81</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC135" s="2"/>
       <c r="AD135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18473,7 +18447,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -18484,13 +18458,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>650</v>
+        <v>274</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>81</v>
@@ -18512,19 +18486,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>651</v>
+        <v>275</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>652</v>
+        <v>276</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18534,7 +18508,7 @@
         <v>81</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>81</v>
@@ -18573,7 +18547,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18594,7 +18568,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18608,7 +18582,7 @@
         <v>653</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18723,7 +18697,7 @@
         <v>654</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18793,16 +18767,16 @@
         <v>81</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF138" t="s" s="2">
         <v>118</v>
@@ -18840,42 +18814,42 @@
         <v>655</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>503</v>
+        <v>284</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>81</v>
@@ -18924,19 +18898,19 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>505</v>
+        <v>288</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>81</v>
@@ -18945,7 +18919,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -18959,7 +18933,7 @@
         <v>656</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18967,7 +18941,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>91</v>
@@ -18982,20 +18956,18 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>560</v>
+        <v>292</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>561</v>
+        <v>293</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>81</v>
       </c>
@@ -19019,13 +18991,13 @@
         <v>81</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19043,10 +19015,10 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>559</v>
+        <v>295</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>91</v>
@@ -19061,13 +19033,13 @@
         <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -19078,7 +19050,7 @@
         <v>657</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19098,19 +19070,21 @@
         <v>81</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+      <c r="O141" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>81</v>
       </c>
@@ -19134,13 +19108,11 @@
         <v>81</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -19158,7 +19130,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19170,7 +19142,7 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
@@ -19179,7 +19151,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -19193,18 +19165,18 @@
         <v>658</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>81</v>
@@ -19213,21 +19185,21 @@
         <v>81</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>81</v>
       </c>
@@ -19263,31 +19235,31 @@
         <v>81</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>81</v>
@@ -19296,7 +19268,7 @@
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>81</v>
@@ -19310,7 +19282,7 @@
         <v>659</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19321,7 +19293,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>81</v>
@@ -19333,19 +19305,19 @@
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19382,23 +19354,25 @@
         <v>81</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC143" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>81</v>
@@ -19413,7 +19387,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -19427,10 +19401,10 @@
         <v>660</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19455,10 +19429,10 @@
         <v>144</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>245</v>
@@ -19474,7 +19448,7 @@
         <v>81</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>81</v>
@@ -19489,13 +19463,11 @@
         <v>81</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>81</v>
@@ -19548,7 +19520,7 @@
         <v>661</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19663,7 +19635,7 @@
         <v>662</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19780,7 +19752,7 @@
         <v>663</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19899,7 +19871,7 @@
         <v>664</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20016,7 +19988,7 @@
         <v>665</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20078,7 +20050,7 @@
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20131,7 +20103,7 @@
         <v>666</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20248,7 +20220,7 @@
         <v>667</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20362,16 +20334,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
         <v>668</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>81</v>
       </c>
@@ -20383,7 +20353,7 @@
         <v>91</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>81</v>
@@ -20392,19 +20362,19 @@
         <v>92</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>81</v>
@@ -20429,11 +20399,13 @@
         <v>81</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y152" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z152" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>81</v>
@@ -20451,13 +20423,13 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>81</v>
@@ -20472,7 +20444,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -20486,7 +20458,7 @@
         <v>669</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20506,19 +20478,23 @@
         <v>81</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>81</v>
       </c>
@@ -20554,19 +20530,17 @@
         <v>81</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="AC153" s="2"/>
       <c r="AD153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20578,22 +20552,22 @@
         <v>81</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" hidden="true">
@@ -20601,18 +20575,20 @@
         <v>670</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="D154" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>81</v>
@@ -20621,21 +20597,23 @@
         <v>81</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>111</v>
+        <v>384</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>112</v>
+        <v>566</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>81</v>
       </c>
@@ -20671,46 +20649,46 @@
         <v>81</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" hidden="true">
@@ -20718,7 +20696,7 @@
         <v>671</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20738,23 +20716,19 @@
         <v>81</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>81</v>
       </c>
@@ -20802,7 +20776,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20814,7 +20788,7 @@
         <v>81</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>81</v>
@@ -20823,7 +20797,7 @@
         <v>81</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -20837,18 +20811,18 @@
         <v>672</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>81</v>
@@ -20857,19 +20831,19 @@
         <v>81</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>294</v>
+        <v>114</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20907,31 +20881,31 @@
         <v>81</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>295</v>
+        <v>118</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>81</v>
@@ -20940,7 +20914,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -20949,12 +20923,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
         <v>673</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20968,7 +20942,7 @@
         <v>91</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>81</v>
@@ -20977,17 +20951,19 @@
         <v>92</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>299</v>
+        <v>397</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O157" t="s" s="2">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21012,11 +20988,13 @@
         <v>81</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y157" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z157" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>81</v>
@@ -21034,7 +21012,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21055,7 +21033,7 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
@@ -21069,7 +21047,7 @@
         <v>674</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21086,28 +21064,30 @@
         <v>81</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J158" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q158" s="2"/>
+      <c r="Q158" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="R158" t="s" s="2">
         <v>81</v>
       </c>
@@ -21127,13 +21107,13 @@
         <v>81</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>81</v>
@@ -21151,7 +21131,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21172,7 +21152,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>311</v>
+        <v>411</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21181,12 +21161,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>675</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21200,7 +21180,7 @@
         <v>91</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>81</v>
@@ -21209,19 +21189,17 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21231,7 +21209,7 @@
         <v>81</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>81</v>
+        <v>676</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>81</v>
@@ -21270,7 +21248,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21291,7 +21269,7 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -21300,12 +21278,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21319,7 +21297,7 @@
         <v>91</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>81</v>
@@ -21328,19 +21306,17 @@
         <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>251</v>
+        <v>420</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
@@ -21350,7 +21326,7 @@
         <v>81</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>81</v>
@@ -21389,7 +21365,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>255</v>
+        <v>424</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21398,7 +21374,7 @@
         <v>91</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>103</v>
@@ -21410,7 +21386,7 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
@@ -21419,12 +21395,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>564</v>
+        <v>637</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21438,7 +21414,7 @@
         <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>81</v>
@@ -21447,19 +21423,19 @@
         <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>565</v>
+        <v>166</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>566</v>
+        <v>427</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>567</v>
+        <v>428</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>568</v>
+        <v>429</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>81</v>
@@ -21469,7 +21445,7 @@
         <v>81</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>81</v>
+        <v>676</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>81</v>
@@ -21496,17 +21472,19 @@
         <v>81</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AC161" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>564</v>
+        <v>431</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21524,28 +21502,26 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>81</v>
       </c>
@@ -21563,22 +21539,22 @@
         <v>81</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>384</v>
+        <v>232</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>81</v>
@@ -21603,13 +21579,13 @@
         <v>81</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>81</v>
@@ -21627,7 +21603,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21636,7 +21612,7 @@
         <v>91</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>103</v>
@@ -21645,35 +21621,35 @@
         <v>81</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>574</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>81</v>
@@ -21685,16 +21661,20 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
       </c>
@@ -21718,13 +21698,13 @@
         <v>81</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>81</v>
@@ -21742,46 +21722,46 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>81</v>
+        <v>450</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -21800,18 +21780,20 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
       </c>
@@ -21847,19 +21829,19 @@
         <v>81</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>118</v>
+        <v>577</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21871,7 +21853,7 @@
         <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>81</v>
@@ -21880,7 +21862,7 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -21889,14 +21871,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C165" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
       </c>
@@ -21908,7 +21892,7 @@
         <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>81</v>
@@ -21917,19 +21901,19 @@
         <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>397</v>
+        <v>684</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>398</v>
+        <v>685</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>399</v>
+        <v>553</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>400</v>
+        <v>554</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -21978,13 +21962,13 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>401</v>
+        <v>550</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>81</v>
@@ -21999,7 +21983,7 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -22010,10 +21994,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22030,30 +22014,26 @@
         <v>81</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>404</v>
+        <v>106</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="N166" s="2"/>
-      <c r="O166" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q166" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="Q166" s="2"/>
       <c r="R166" t="s" s="2">
         <v>81</v>
       </c>
@@ -22073,13 +22053,13 @@
         <v>81</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>81</v>
@@ -22097,7 +22077,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>410</v>
+        <v>108</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22109,7 +22089,7 @@
         <v>81</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>81</v>
@@ -22118,7 +22098,7 @@
         <v>81</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22129,21 +22109,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>81</v>
@@ -22152,21 +22132,21 @@
         <v>81</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>413</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>81</v>
       </c>
@@ -22175,7 +22155,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>684</v>
+        <v>81</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -22214,19 +22194,19 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>417</v>
+        <v>118</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>81</v>
@@ -22235,7 +22215,7 @@
         <v>81</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
@@ -22246,43 +22226,45 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I168" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J168" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O168" t="s" s="2">
-        <v>422</v>
+        <v>194</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22292,7 +22274,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -22331,19 +22313,19 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>81</v>
@@ -22352,7 +22334,7 @@
         <v>81</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
@@ -22363,10 +22345,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22374,7 +22356,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>91</v>
@@ -22389,19 +22371,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22411,7 +22393,7 @@
         <v>81</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>684</v>
+        <v>81</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>81</v>
@@ -22426,13 +22408,13 @@
         <v>81</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -22450,10 +22432,10 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>431</v>
+        <v>559</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>91</v>
@@ -22468,13 +22450,13 @@
         <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>81</v>
+        <v>563</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>418</v>
+        <v>266</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22482,10 +22464,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22508,20 +22490,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>588</v>
+        <v>106</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>81</v>
       </c>
@@ -22545,13 +22523,13 @@
         <v>81</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -22569,7 +22547,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>587</v>
+        <v>108</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22578,10 +22556,10 @@
         <v>91</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>81</v>
@@ -22590,7 +22568,7 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
@@ -22601,14 +22579,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -22627,20 +22605,18 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>592</v>
+        <v>112</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>593</v>
+        <v>113</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>81</v>
       </c>
@@ -22664,31 +22640,31 @@
         <v>81</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>591</v>
+        <v>118</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22700,30 +22676,30 @@
         <v>81</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22743,22 +22719,22 @@
         <v>81</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>595</v>
+        <v>243</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>596</v>
+        <v>244</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>495</v>
+        <v>245</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>496</v>
+        <v>246</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -22795,19 +22771,17 @@
         <v>81</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AC172" s="2"/>
       <c r="AD172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>594</v>
+        <v>248</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22828,7 +22802,7 @@
         <v>81</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -22839,13 +22813,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>691</v>
+        <v>274</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>81</v>
@@ -22867,19 +22841,19 @@
         <v>92</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>492</v>
+        <v>144</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>692</v>
+        <v>275</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>693</v>
+        <v>276</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>553</v>
+        <v>245</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>554</v>
+        <v>246</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>81</v>
@@ -22889,7 +22863,7 @@
         <v>81</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>81</v>
+        <v>694</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>81</v>
@@ -22928,7 +22902,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22949,7 +22923,7 @@
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>555</v>
+        <v>249</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>
@@ -22960,10 +22934,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23075,10 +23049,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23148,16 +23122,16 @@
         <v>81</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF175" t="s" s="2">
         <v>118</v>
@@ -23192,45 +23166,45 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J176" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>503</v>
+        <v>284</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23279,19 +23253,19 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>505</v>
+        <v>288</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>81</v>
@@ -23300,7 +23274,7 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
@@ -23311,10 +23285,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23322,7 +23296,7 @@
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>91</v>
@@ -23337,20 +23311,18 @@
         <v>92</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>560</v>
+        <v>292</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>561</v>
+        <v>293</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>81</v>
       </c>
@@ -23374,13 +23346,13 @@
         <v>81</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>81</v>
@@ -23398,10 +23370,10 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>559</v>
+        <v>295</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>91</v>
@@ -23416,13 +23388,13 @@
         <v>81</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>563</v>
+        <v>81</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23430,10 +23402,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23453,19 +23425,21 @@
         <v>81</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+      <c r="O178" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>81</v>
       </c>
@@ -23489,13 +23463,11 @@
         <v>81</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>81</v>
@@ -23513,7 +23485,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23525,7 +23497,7 @@
         <v>81</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>81</v>
@@ -23534,7 +23506,7 @@
         <v>81</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
@@ -23545,21 +23517,21 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>81</v>
@@ -23568,21 +23540,21 @@
         <v>81</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
       </c>
@@ -23618,31 +23590,31 @@
         <v>81</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>118</v>
+        <v>310</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>81</v>
@@ -23651,7 +23623,7 @@
         <v>81</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
@@ -23662,10 +23634,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23676,7 +23648,7 @@
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>81</v>
@@ -23688,19 +23660,19 @@
         <v>92</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>144</v>
+        <v>314</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>246</v>
+        <v>318</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -23737,23 +23709,25 @@
         <v>81</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AC180" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>81</v>
@@ -23768,7 +23742,7 @@
         <v>81</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>81</v>
@@ -23777,16 +23751,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>81</v>
       </c>
@@ -23798,7 +23770,7 @@
         <v>91</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>81</v>
@@ -23807,19 +23779,19 @@
         <v>92</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
@@ -23829,7 +23801,7 @@
         <v>81</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>702</v>
+        <v>81</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>81</v>
@@ -23868,13 +23840,13 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>81</v>
@@ -23889,7 +23861,7 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>81</v>
@@ -23903,7 +23875,7 @@
         <v>703</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23923,19 +23895,23 @@
         <v>81</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>106</v>
+        <v>566</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
       </c>
@@ -23983,7 +23959,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -23995,22 +23971,22 @@
         <v>81</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="183" hidden="true">
@@ -24018,18 +23994,18 @@
         <v>704</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>616</v>
+        <v>570</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>81</v>
@@ -24041,18 +24017,20 @@
         <v>81</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>112</v>
+        <v>571</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>113</v>
+        <v>572</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
       </c>
@@ -24076,43 +24054,43 @@
         <v>81</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>118</v>
+        <v>570</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>81</v>
@@ -24121,7 +24099,7 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
@@ -24135,18 +24113,18 @@
         <v>705</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>81</v>
@@ -24155,22 +24133,22 @@
         <v>81</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>284</v>
+        <v>575</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>285</v>
+        <v>576</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>286</v>
+        <v>445</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>287</v>
+        <v>446</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -24195,13 +24173,13 @@
         <v>81</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>81</v>
@@ -24219,13 +24197,13 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>288</v>
+        <v>574</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>81</v>
@@ -24237,16 +24215,16 @@
         <v>81</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>81</v>
+        <v>449</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>81</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" hidden="true">
@@ -24254,7 +24232,7 @@
         <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>620</v>
+        <v>577</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24265,7 +24243,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>81</v>
@@ -24274,21 +24252,23 @@
         <v>81</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>292</v>
+        <v>578</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>293</v>
+        <v>579</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24336,13 +24316,13 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>295</v>
+        <v>577</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>81</v>
@@ -24357,963 +24337,17 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>296</v>
+        <v>498</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="P186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y186" s="2"/>
-      <c r="Z186" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO193" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO193">
+  <autoFilter ref="A1:AO185">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25323,7 +24357,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI192">
+  <conditionalFormatting sqref="A2:AI184">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-kco.xlsx
@@ -884,7 +884,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="251952002"/&gt;
   &lt;display value="Transfer coefficient (respiratory measure) (observable entity)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -1880,7 +1880,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="TODO"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
@@ -2182,7 +2182,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="1078210003"/&gt;
   &lt;display value="Z-score calculation technique (qualifier value)"/&gt;
 &lt;/valueCoding&gt;</t>
